--- a/Excel/LegacyGradeConfig.xlsx
+++ b/Excel/LegacyGradeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -1343,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>17</v>
@@ -1384,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>25</v>
@@ -1425,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>17</v>
@@ -1466,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>25</v>
@@ -1507,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>34</v>
@@ -1548,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>17</v>
@@ -1589,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>34</v>
@@ -1630,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>34</v>
@@ -1677,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>45</v>
@@ -1718,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>46</v>
@@ -1759,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>45</v>
@@ -1800,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>46</v>
@@ -1841,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>47</v>
@@ -1882,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>45</v>
@@ -1923,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>47</v>
@@ -1964,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>47</v>
@@ -2014,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>48</v>
@@ -2055,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>49</v>
@@ -2096,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>48</v>
@@ -2137,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>49</v>
@@ -2178,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>50</v>
@@ -2219,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>48</v>
@@ -2260,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>50</v>
@@ -2301,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>50</v>
